--- a/data/C GST.xlsx
+++ b/data/C GST.xlsx
@@ -581,7 +581,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="72">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -860,14 +860,6 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -901,9 +893,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>266400</xdr:colOff>
+      <xdr:colOff>266040</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>149760</xdr:rowOff>
+      <xdr:rowOff>149400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -916,47 +908,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9719280" y="9410760"/>
-          <a:ext cx="9360" cy="9360"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>235440</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1066680</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>578160</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 4" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10795680" y="12744360"/>
-          <a:ext cx="1841400" cy="590400"/>
+          <a:off x="9718560" y="9410760"/>
+          <a:ext cx="9000" cy="9000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1661,11 +1614,11 @@
       <c r="H47" s="46"/>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="70" t="s">
+      <c r="A48" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="71"/>
-      <c r="C48" s="71"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
       <c r="D48" s="13"/>
       <c r="E48" s="13"/>
       <c r="F48" s="14" t="s">
@@ -1692,23 +1645,23 @@
       <c r="C50" s="64"/>
       <c r="D50" s="64"/>
       <c r="E50" s="64"/>
-      <c r="F50" s="72" t="s">
+      <c r="F50" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="G50" s="72"/>
-      <c r="H50" s="72"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="73" t="s">
+      <c r="A51" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="73"/>
-      <c r="C51" s="73"/>
-      <c r="D51" s="73"/>
-      <c r="E51" s="73"/>
-      <c r="F51" s="73"/>
-      <c r="G51" s="73"/>
-      <c r="H51" s="73"/>
+      <c r="B51" s="71"/>
+      <c r="C51" s="71"/>
+      <c r="D51" s="71"/>
+      <c r="E51" s="71"/>
+      <c r="F51" s="71"/>
+      <c r="G51" s="71"/>
+      <c r="H51" s="71"/>
     </row>
     <row r="52" customFormat="false" ht="0.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/data/C GST.xlsx
+++ b/data/C GST.xlsx
@@ -23,24 +23,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t xml:space="preserve">TAX INVOICE</t>
   </si>
   <si>
-    <t xml:space="preserve"> ADOODS GARMENTS &amp; SPORTS</t>
+    <t xml:space="preserve"> MAX GARMENTS &amp; SPORTS</t>
   </si>
   <si>
     <t xml:space="preserve">ALL KINDS OF T-SHIRT MANUFACTURE</t>
   </si>
   <si>
-    <t xml:space="preserve">88-1/50M, 1st FLOOR NEAR SRINIVASA THEATRE, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULAVARSANDHAI ROAD, HOSUR - 635 109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTIN :33DJRPP6135G1ZW</t>
+    <t xml:space="preserve">890/50M, 10st FLOOR NEAR Vijay THEATRE, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULAVARSANDHAI ROAD, chennai – 600 000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Black"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">GSTIN :3335G1ZW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Black"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">DJRPP61</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">STATE: TAMIL NADU   CODE: 33</t>
@@ -54,7 +72,7 @@
         <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">                                             Website : adoodshosur@gmail.com                    PHONE:-  </t>
+      <t xml:space="preserve">                                             Website : Example.com                    PHONE:-  </t>
     </r>
     <r>
       <rPr>
@@ -64,7 +82,7 @@
         <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> 9514109080 </t>
+      <t xml:space="preserve"> 9000000000 </t>
     </r>
   </si>
   <si>
@@ -79,7 +97,7 @@
         <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">                                                   Email : sales@adoods.com                                        </t>
+      <t xml:space="preserve">                                                   Email : sales@example.com                                        </t>
     </r>
     <r>
       <rPr>
@@ -89,8 +107,17 @@
         <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> 6382208004</t>
+      <t xml:space="preserve"> 6</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Black"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">000000000</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">BUYER DETAILS</t>
@@ -99,7 +126,7 @@
     <t xml:space="preserve">INVOICE DETAILS</t>
   </si>
   <si>
-    <t xml:space="preserve">Unnathi hr solution</t>
+    <t xml:space="preserve">Stalin hr solution</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -121,10 +148,25 @@
     <t xml:space="preserve">Mobile: 8098374113, 9865757486</t>
   </si>
   <si>
-    <t xml:space="preserve">\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gst no: 33AEBPL4738H1ZN</t>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gst no: 33A1ZN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">EBPL4738H</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">SL.NO</t>
@@ -162,7 +204,7 @@
         <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">ADVANSH</t>
+      <t xml:space="preserve">Stalin</t>
     </r>
     <r>
       <rPr>
@@ -207,7 +249,7 @@
     <t xml:space="preserve">Tax Amount (in words) :</t>
   </si>
   <si>
-    <t xml:space="preserve">    GP  :-9514109080 _6382208004</t>
+    <t xml:space="preserve">    GP  :-9000000000 _6000000000</t>
   </si>
   <si>
     <t xml:space="preserve">BANK DETAILS:</t>
@@ -219,28 +261,19 @@
     <t xml:space="preserve">Bank Name</t>
   </si>
   <si>
-    <t xml:space="preserve">K V B </t>
-  </si>
-  <si>
     <t xml:space="preserve">THROUGH :</t>
   </si>
   <si>
     <t xml:space="preserve">A/C. No</t>
   </si>
   <si>
-    <t xml:space="preserve">.            1607135000011387</t>
-  </si>
-  <si>
     <t xml:space="preserve">Branch &amp; IFSC Code</t>
   </si>
   <si>
-    <t xml:space="preserve">KVBL0001607</t>
-  </si>
-  <si>
     <t xml:space="preserve">Declaration</t>
   </si>
   <si>
-    <t xml:space="preserve">for ADOODS GARMENTS</t>
+    <t xml:space="preserve">for Example GARMENTS</t>
   </si>
   <si>
     <t xml:space="preserve">We declare that the Invoice shows the actual price of the goods</t>
@@ -265,7 +298,7 @@
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -325,6 +358,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Black"/>
+      <family val="0"/>
+    </font>
+    <font>
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Arial Black"/>
@@ -337,6 +376,12 @@
       <name val="Arial Black"/>
       <family val="0"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Black"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="18"/>
@@ -359,6 +404,12 @@
       <name val="Arial Black"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
     </font>
     <font>
       <i val="true"/>
@@ -606,11 +657,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -618,7 +669,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -646,7 +697,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -662,7 +713,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -730,7 +781,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -754,7 +805,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -888,14 +939,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>257040</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>140400</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>-720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>266040</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>149400</xdr:rowOff>
+      <xdr:colOff>265680</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -909,7 +960,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9718560" y="9410760"/>
-          <a:ext cx="9000" cy="9000"/>
+          <a:ext cx="8640" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1005,7 +1056,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -1029,7 +1080,7 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
@@ -1122,9 +1173,6 @@
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
@@ -1132,7 +1180,7 @@
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -1147,26 +1195,26 @@
     </row>
     <row r="16" s="24" customFormat="true" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>21</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>22</v>
       </c>
       <c r="C16" s="22"/>
       <c r="D16" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="F16" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="G16" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="H16" s="23" t="s">
         <v>26</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1184,7 +1232,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="29"/>
       <c r="D18" s="28"/>
@@ -1195,7 +1243,7 @@
         <v>260</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H18" s="32" t="n">
         <f aca="false">F18*E18</f>
@@ -1288,12 +1336,12 @@
       <c r="G25" s="28"/>
       <c r="H25" s="32"/>
     </row>
-    <row r="26" s="33" customFormat="true" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="33" customFormat="true" ht="15.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="n">
         <v>9</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="28"/>
       <c r="D26" s="28"/>
@@ -1330,7 +1378,7 @@
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="38"/>
       <c r="B29" s="39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="38"/>
@@ -1345,7 +1393,7 @@
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="38"/>
       <c r="B30" s="39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="38"/>
@@ -1371,7 +1419,7 @@
     <row r="32" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="25"/>
       <c r="B32" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="42"/>
       <c r="D32" s="25"/>
@@ -1388,7 +1436,7 @@
       <c r="B33" s="45"/>
       <c r="C33" s="45"/>
       <c r="D33" s="46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" s="46"/>
       <c r="F33" s="46"/>
@@ -1397,7 +1445,7 @@
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -1419,22 +1467,22 @@
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" s="49"/>
       <c r="C36" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="49" t="s">
         <v>36</v>
-      </c>
-      <c r="D36" s="49" t="s">
-        <v>37</v>
       </c>
       <c r="E36" s="49"/>
       <c r="F36" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G36" s="49"/>
       <c r="H36" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1442,16 +1490,16 @@
       <c r="B37" s="52"/>
       <c r="C37" s="49"/>
       <c r="D37" s="52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F37" s="52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G37" s="52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H37" s="50"/>
     </row>
@@ -1485,7 +1533,7 @@
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="59"/>
       <c r="C39" s="60" t="n">
@@ -1519,7 +1567,7 @@
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -1536,7 +1584,7 @@
       <c r="D42" s="64"/>
       <c r="E42" s="64"/>
       <c r="F42" s="64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G42" s="64"/>
       <c r="H42" s="65"/>
@@ -1546,7 +1594,7 @@
       <c r="B43" s="45"/>
       <c r="C43" s="62"/>
       <c r="D43" s="66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
@@ -1555,33 +1603,29 @@
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="14"/>
       <c r="D44" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E44" s="11"/>
-      <c r="F44" s="67" t="s">
-        <v>45</v>
-      </c>
+      <c r="F44" s="67"/>
       <c r="G44" s="67"/>
       <c r="H44" s="67"/>
     </row>
     <row r="45" s="68" customFormat="true" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="14"/>
       <c r="D45" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E45" s="11"/>
-      <c r="F45" s="14" t="s">
-        <v>48</v>
-      </c>
+      <c r="F45" s="14"/>
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
     </row>
@@ -1590,32 +1634,30 @@
       <c r="B46" s="64"/>
       <c r="C46" s="65"/>
       <c r="D46" s="63" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E46" s="63"/>
-      <c r="F46" s="69" t="s">
-        <v>50</v>
-      </c>
+      <c r="F46" s="69"/>
       <c r="G46" s="69"/>
       <c r="H46" s="69"/>
     </row>
     <row r="47" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="47" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B47" s="45"/>
       <c r="C47" s="45"/>
       <c r="D47" s="45"/>
       <c r="E47" s="45"/>
       <c r="F47" s="46" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G47" s="46"/>
       <c r="H47" s="46"/>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
@@ -1629,7 +1671,7 @@
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
@@ -1646,14 +1688,14 @@
       <c r="D50" s="64"/>
       <c r="E50" s="64"/>
       <c r="F50" s="70" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G50" s="70"/>
       <c r="H50" s="70"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="71" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B51" s="71"/>
       <c r="C51" s="71"/>
@@ -1713,6 +1755,9 @@
     <mergeCell ref="F48:H49"/>
     <mergeCell ref="F50:H50"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A9" r:id="rId1" display="sales@example"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.708333333333333" right="0.433333333333333" top="0.511805555555556" bottom="0.236111111111111" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="61" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1720,6 +1765,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>